--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -670,7 +670,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -685,7 +685,7 @@
     <t>MedicationStatement.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -715,7 +715,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -913,7 +913,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1017,7 +1017,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1058,7 +1058,7 @@
     <t>MedicationStatement.dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1390,7 +1390,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1405,7 +1405,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.84375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationstatement.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationStatement</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -670,7 +670,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -685,7 +685,7 @@
     <t>MedicationStatement.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -715,7 +715,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
 </t>
   </si>
   <si>
@@ -913,7 +913,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1017,7 +1017,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -1058,7 +1058,7 @@
     <t>MedicationStatement.dosage</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage|1.3.0-dev}
+    <t xml:space="preserve">Dosage {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDosage}
 </t>
   </si>
   <si>
@@ -1390,7 +1390,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1405,7 +1405,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.84375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
